--- a/从零开始学Slots/从零开始学Slots-09-数值篇-Scatter(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-09-数值篇-Scatter(1).xlsx
@@ -9031,6 +9031,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N193" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -10239,5 +10242,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:S90" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-09-数值篇-Scatter(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-09-数值篇-Scatter(1).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="217">
   <si>
     <r>
       <rPr>
@@ -7822,7 +7822,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7961,6 +7961,14 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -10153,8 +10161,8 @@
       <c r="D65" s="17"/>
     </row>
     <row r="66" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="20" t="s">
-        <v>210</v>
+      <c r="A66" s="35">
+        <v>3</v>
       </c>
       <c r="B66" s="29" t="str">
         <f aca="false">IF(G23=4563,"✓","✗")</f>
@@ -10185,8 +10193,8 @@
         <f aca="false">IF(ABS(B47-1.2756)&lt;0.0005,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="C68" s="17" t="s">
-        <v>215</v>
+      <c r="C68" s="36">
+        <v>0.6185</v>
       </c>
       <c r="D68" s="17"/>
     </row>

--- a/从零开始学Slots/从零开始学Slots-09-数值篇-Scatter(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-09-数值篇-Scatter(1).xlsx
@@ -7633,12 +7633,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.00%"/>
+    <numFmt numFmtId="169" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -7822,7 +7823,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7968,6 +7969,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9402,7 +9415,7 @@
         <f aca="false">PRODUCT(3*3*3*13*13)</f>
         <v>4563</v>
       </c>
-      <c r="H23" s="23" t="n">
+      <c r="H23" s="37" t="n">
         <f aca="false">G23/$B$9</f>
         <v>0.00435161590576172</v>
       </c>
@@ -9430,7 +9443,7 @@
         <f aca="false">PRODUCT(3*3*13*3*13)</f>
         <v>4563</v>
       </c>
-      <c r="H24" s="23" t="n">
+      <c r="H24" s="37" t="n">
         <f aca="false">G24/$B$9</f>
         <v>0.00435161590576172</v>
       </c>
@@ -9458,7 +9471,7 @@
         <f aca="false">PRODUCT(3*3*13*13*3)</f>
         <v>4563</v>
       </c>
-      <c r="H25" s="23" t="n">
+      <c r="H25" s="37" t="n">
         <f aca="false">G25/$B$9</f>
         <v>0.00435161590576172</v>
       </c>
@@ -9486,7 +9499,7 @@
         <f aca="false">PRODUCT(3*13*3*3*13)</f>
         <v>4563</v>
       </c>
-      <c r="H26" s="23" t="n">
+      <c r="H26" s="37" t="n">
         <f aca="false">G26/$B$9</f>
         <v>0.00435161590576172</v>
       </c>
@@ -9514,7 +9527,7 @@
         <f aca="false">PRODUCT(3*13*3*13*3)</f>
         <v>4563</v>
       </c>
-      <c r="H27" s="23" t="n">
+      <c r="H27" s="37" t="n">
         <f aca="false">G27/$B$9</f>
         <v>0.00435161590576172</v>
       </c>
@@ -9542,7 +9555,7 @@
         <f aca="false">PRODUCT(3*13*13*3*3)</f>
         <v>4563</v>
       </c>
-      <c r="H28" s="23" t="n">
+      <c r="H28" s="37" t="n">
         <f aca="false">G28/$B$9</f>
         <v>0.00435161590576172</v>
       </c>
@@ -9570,7 +9583,7 @@
         <f aca="false">PRODUCT(13*3*3*3*13)</f>
         <v>4563</v>
       </c>
-      <c r="H29" s="23" t="n">
+      <c r="H29" s="37" t="n">
         <f aca="false">G29/$B$9</f>
         <v>0.00435161590576172</v>
       </c>
@@ -9598,7 +9611,7 @@
         <f aca="false">PRODUCT(13*3*3*13*3)</f>
         <v>4563</v>
       </c>
-      <c r="H30" s="23" t="n">
+      <c r="H30" s="37" t="n">
         <f aca="false">G30/$B$9</f>
         <v>0.00435161590576172</v>
       </c>
@@ -9626,7 +9639,7 @@
         <f aca="false">PRODUCT(13*3*13*3*3)</f>
         <v>4563</v>
       </c>
-      <c r="H31" s="23" t="n">
+      <c r="H31" s="37" t="n">
         <f aca="false">G31/$B$9</f>
         <v>0.00435161590576172</v>
       </c>
@@ -9654,7 +9667,7 @@
         <f aca="false">PRODUCT(13*13*3*3*3)</f>
         <v>4563</v>
       </c>
-      <c r="H32" s="23" t="n">
+      <c r="H32" s="37" t="n">
         <f aca="false">G32/$B$9</f>
         <v>0.00435161590576172</v>
       </c>
@@ -9682,7 +9695,7 @@
         <f aca="false">PRODUCT(3*3*3*3*13)</f>
         <v>1053</v>
       </c>
-      <c r="H33" s="23" t="n">
+      <c r="H33" s="37" t="n">
         <f aca="false">G33/$B$9</f>
         <v>0.00100421905517578</v>
       </c>
@@ -9710,7 +9723,7 @@
         <f aca="false">PRODUCT(3*3*3*13*3)</f>
         <v>1053</v>
       </c>
-      <c r="H34" s="23" t="n">
+      <c r="H34" s="37" t="n">
         <f aca="false">G34/$B$9</f>
         <v>0.00100421905517578</v>
       </c>
@@ -9738,7 +9751,7 @@
         <f aca="false">PRODUCT(3*3*13*3*3)</f>
         <v>1053</v>
       </c>
-      <c r="H35" s="23" t="n">
+      <c r="H35" s="37" t="n">
         <f aca="false">G35/$B$9</f>
         <v>0.00100421905517578</v>
       </c>
@@ -9766,7 +9779,7 @@
         <f aca="false">PRODUCT(3*13*3*3*3)</f>
         <v>1053</v>
       </c>
-      <c r="H36" s="23" t="n">
+      <c r="H36" s="37" t="n">
         <f aca="false">G36/$B$9</f>
         <v>0.00100421905517578</v>
       </c>
@@ -9794,7 +9807,7 @@
         <f aca="false">PRODUCT(13*3*3*3*3)</f>
         <v>1053</v>
       </c>
-      <c r="H37" s="23" t="n">
+      <c r="H37" s="37" t="n">
         <f aca="false">G37/$B$9</f>
         <v>0.00100421905517578</v>
       </c>
@@ -9822,7 +9835,7 @@
         <f aca="false">PRODUCT(3*3*3*3*3)</f>
         <v>243</v>
       </c>
-      <c r="H38" s="23" t="n">
+      <c r="H38" s="37" t="n">
         <f aca="false">G38/$B$9</f>
         <v>0.000231742858886719</v>
       </c>
@@ -9835,7 +9848,7 @@
         <f aca="false">SUM(G23:G38)</f>
         <v>51138</v>
       </c>
-      <c r="H39" s="25" t="n">
+      <c r="H39" s="38" t="n">
         <f aca="false">G39/$B$9</f>
         <v>0.0487689971923828</v>
       </c>
@@ -9890,7 +9903,7 @@
       <c r="A44" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B44" s="23" t="n">
+      <c r="B44" s="37" t="n">
         <f aca="false">(SUM(G23:G38))/$B$9</f>
         <v>0.0487689971923828</v>
       </c>
@@ -9941,7 +9954,7 @@
       <c r="A48" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="B48" s="28" t="n">
+      <c r="B48" s="39" t="n">
         <f aca="false">B46/B47</f>
         <v>0.515130134838507</v>
       </c>
@@ -9998,7 +10011,7 @@
       <c r="A53" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B53" s="23" t="n">
+      <c r="B53" s="37" t="n">
         <f aca="false">B44</f>
         <v>0.0487689971923828</v>
       </c>
